--- a/बजेट माग estimate/nagar bhaipari and estimate misc/तल्लो नंग्लेद्वारे चिहानपाटी/devithaan.xlsx
+++ b/बजेट माग estimate/nagar bhaipari and estimate misc/तल्लो नंग्लेद्वारे चिहानपाटी/devithaan.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155D5561-A1B1-4765-A9F3-973D46A2EFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
@@ -238,10 +237,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -415,9 +414,9 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -429,7 +428,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -453,14 +452,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -479,7 +478,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -494,7 +493,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -532,7 +531,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -543,24 +542,6 @@
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -581,14 +562,32 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2" xfId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="5"/>
+    <cellStyle name="Percent 2" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -604,7 +603,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -698,7 +697,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -757,7 +756,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -821,9 +820,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -861,9 +860,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -898,7 +897,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -933,7 +932,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1106,135 +1105,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S82"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="19"/>
+    <col min="1" max="1" width="4.6640625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="19"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="19"/>
+    <col min="9" max="9" width="9.5546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.109375" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="19"/>
+    <col min="17" max="16384" width="9.109375" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-    </row>
-    <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+    </row>
+    <row r="2" spans="1:16" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-    </row>
-    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="53" t="s">
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-    </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+    </row>
+    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="49" t="s">
+      <c r="H6" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="56" t="s">
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="57" t="s">
+      <c r="H7" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
-    </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+    </row>
+    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>6</v>
       </c>
@@ -1269,7 +1268,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="188.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="188.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16">
         <v>1</v>
       </c>
@@ -1286,7 +1285,7 @@
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="16"/>
       <c r="B10" s="32" t="s">
         <v>30</v>
@@ -1326,7 +1325,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="16"/>
       <c r="B11" s="32"/>
       <c r="C11" s="17">
@@ -1356,7 +1355,7 @@
       <c r="O11" s="36"/>
       <c r="P11" s="36"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
       <c r="B12" s="32"/>
       <c r="C12" s="17">
@@ -1385,7 +1384,7 @@
       <c r="O12" s="36"/>
       <c r="P12" s="36"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="16"/>
       <c r="B13" s="32" t="s">
         <v>51</v>
@@ -1416,7 +1415,7 @@
       <c r="O13" s="36"/>
       <c r="P13" s="36"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="16"/>
       <c r="B14" s="32" t="str">
         <f>B23</f>
@@ -1451,7 +1450,7 @@
       <c r="O14" s="36"/>
       <c r="P14" s="36"/>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="34" t="s">
         <v>17</v>
@@ -1476,7 +1475,7 @@
       </c>
       <c r="K15" s="5"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16" s="32" t="s">
         <v>24</v>
@@ -1494,7 +1493,7 @@
       </c>
       <c r="K16" s="17"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="16"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -1507,7 +1506,7 @@
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
     </row>
-    <row r="18" spans="1:16" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A18" s="16">
         <v>2</v>
       </c>
@@ -1524,7 +1523,7 @@
       <c r="J18" s="17"/>
       <c r="K18" s="17"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
       <c r="B19" s="32" t="str">
         <f>B10</f>
@@ -1566,7 +1565,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="16"/>
       <c r="B20" s="32"/>
       <c r="C20" s="17">
@@ -1596,7 +1595,7 @@
       <c r="O20" s="36"/>
       <c r="P20" s="36"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="16"/>
       <c r="B21" s="32"/>
       <c r="C21" s="17">
@@ -1626,7 +1625,7 @@
       <c r="O21" s="36"/>
       <c r="P21" s="36"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="32" t="s">
         <v>51</v>
@@ -1657,7 +1656,7 @@
       <c r="O22" s="36"/>
       <c r="P22" s="36"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="16"/>
       <c r="B23" s="32" t="str">
         <f>B35</f>
@@ -1691,7 +1690,7 @@
       <c r="O23" s="36"/>
       <c r="P23" s="36"/>
     </row>
-    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="34" t="s">
         <v>17</v>
@@ -1716,7 +1715,7 @@
       </c>
       <c r="K24" s="5"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="16"/>
       <c r="B25" s="32" t="s">
         <v>24</v>
@@ -1734,7 +1733,7 @@
       </c>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -1747,7 +1746,7 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
     </row>
-    <row r="27" spans="1:16" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A27" s="16">
         <v>3</v>
       </c>
@@ -1764,7 +1763,7 @@
       <c r="J27" s="17"/>
       <c r="K27" s="17"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="B28" s="32" t="str">
         <f>B19</f>
@@ -1806,7 +1805,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="16"/>
       <c r="B29" s="32"/>
       <c r="C29" s="17">
@@ -1835,7 +1834,7 @@
       <c r="O29" s="36"/>
       <c r="P29" s="36"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="16"/>
       <c r="B30" s="32"/>
       <c r="C30" s="17">
@@ -1865,7 +1864,7 @@
       <c r="O30" s="36"/>
       <c r="P30" s="36"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="B31" s="32"/>
       <c r="C31" s="17">
@@ -1894,7 +1893,7 @@
       <c r="O31" s="36"/>
       <c r="P31" s="36"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="16"/>
       <c r="B32" s="32"/>
       <c r="C32" s="17">
@@ -1924,7 +1923,7 @@
       <c r="O32" s="36"/>
       <c r="P32" s="36"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
       <c r="B33" s="32" t="str">
         <f>B22</f>
@@ -1958,7 +1957,7 @@
       <c r="O33" s="36"/>
       <c r="P33" s="36"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="16"/>
       <c r="B34" s="32"/>
       <c r="C34" s="32">
@@ -1987,7 +1986,7 @@
       <c r="O34" s="36"/>
       <c r="P34" s="36"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
       <c r="B35" s="32" t="s">
         <v>53</v>
@@ -2017,7 +2016,7 @@
       <c r="O35" s="36"/>
       <c r="P35" s="36"/>
     </row>
-    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="34" t="s">
         <v>17</v>
@@ -2042,7 +2041,7 @@
       </c>
       <c r="K36" s="5"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="32" t="s">
         <v>33</v>
@@ -2060,7 +2059,7 @@
       </c>
       <c r="K37" s="17"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="16"/>
       <c r="B38" s="32" t="s">
         <v>34</v>
@@ -2078,7 +2077,7 @@
       </c>
       <c r="K38" s="17"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
       <c r="B39" s="32" t="s">
         <v>35</v>
@@ -2096,7 +2095,7 @@
       </c>
       <c r="K39" s="17"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="16"/>
       <c r="B40" s="32" t="s">
         <v>36</v>
@@ -2114,7 +2113,7 @@
       </c>
       <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
       <c r="B41" s="32" t="s">
         <v>40</v>
@@ -2132,7 +2131,7 @@
       </c>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="16"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -2145,7 +2144,7 @@
       <c r="J42" s="17"/>
       <c r="K42" s="17"/>
     </row>
-    <row r="43" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A43" s="16">
         <v>4</v>
       </c>
@@ -2162,7 +2161,7 @@
       <c r="J43" s="17"/>
       <c r="K43" s="17"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="32" t="str">
         <f>B28</f>
@@ -2204,7 +2203,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="32"/>
       <c r="C45" s="17">
@@ -2234,7 +2233,7 @@
       <c r="O45" s="36"/>
       <c r="P45" s="36"/>
     </row>
-    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="34" t="s">
         <v>17</v>
@@ -2259,7 +2258,7 @@
       </c>
       <c r="K46" s="5"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="32" t="s">
         <v>33</v>
@@ -2277,7 +2276,7 @@
       </c>
       <c r="K47" s="17"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="32" t="s">
         <v>34</v>
@@ -2295,7 +2294,7 @@
       </c>
       <c r="K48" s="17"/>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
       <c r="B49" s="32" t="s">
         <v>38</v>
@@ -2313,7 +2312,7 @@
       </c>
       <c r="K49" s="17"/>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
       <c r="B50" s="32" t="s">
         <v>40</v>
@@ -2331,7 +2330,7 @@
       </c>
       <c r="K50" s="17"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
@@ -2344,7 +2343,7 @@
       <c r="J51" s="17"/>
       <c r="K51" s="17"/>
     </row>
-    <row r="52" spans="1:18" s="41" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" s="41" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>5</v>
       </c>
@@ -2369,7 +2368,7 @@
       <c r="J52" s="40"/>
       <c r="K52" s="5"/>
     </row>
-    <row r="53" spans="1:18" s="41" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" s="41" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A53" s="42"/>
       <c r="B53" s="43" t="s">
         <v>54</v>
@@ -2386,11 +2385,11 @@
         <v>6.5</v>
       </c>
       <c r="F53" s="45">
-        <f>PRODUCT(C53:E53)</f>
+        <f t="shared" ref="F53:F58" si="4">PRODUCT(C53:E53)</f>
         <v>118.86619932947272</v>
       </c>
       <c r="G53" s="9">
-        <f>F53</f>
+        <f t="shared" ref="G53:G58" si="5">F53</f>
         <v>118.86619932947272</v>
       </c>
       <c r="H53" s="40"/>
@@ -2398,7 +2397,7 @@
       <c r="J53" s="40"/>
       <c r="K53" s="46"/>
     </row>
-    <row r="54" spans="1:18" s="41" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" s="41" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A54" s="42"/>
       <c r="B54" s="43" t="s">
         <v>55</v>
@@ -2414,11 +2413,11 @@
         <v>6.5</v>
       </c>
       <c r="F54" s="45">
-        <f>PRODUCT(C54:E54)</f>
+        <f t="shared" si="4"/>
         <v>95.092959463578183</v>
       </c>
       <c r="G54" s="9">
-        <f>F54</f>
+        <f t="shared" si="5"/>
         <v>95.092959463578183</v>
       </c>
       <c r="H54" s="40"/>
@@ -2434,7 +2433,7 @@
         <v>47.997657714303543</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="41" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" s="41" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A55" s="42"/>
       <c r="B55" s="43" t="s">
         <v>56</v>
@@ -2450,11 +2449,11 @@
         <v>6.5</v>
       </c>
       <c r="F55" s="45">
-        <f>PRODUCT(C55:E55)</f>
+        <f t="shared" si="4"/>
         <v>47.546479731789091</v>
       </c>
       <c r="G55" s="9">
-        <f>F55</f>
+        <f t="shared" si="5"/>
         <v>47.546479731789091</v>
       </c>
       <c r="H55" s="40"/>
@@ -2462,7 +2461,7 @@
       <c r="J55" s="40"/>
       <c r="K55" s="46"/>
     </row>
-    <row r="56" spans="1:18" s="41" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" s="41" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A56" s="42"/>
       <c r="B56" s="43" t="s">
         <v>57</v>
@@ -2478,11 +2477,11 @@
         <v>6.5</v>
       </c>
       <c r="F56" s="45">
-        <f>PRODUCT(C56:E56)</f>
+        <f t="shared" si="4"/>
         <v>43.584273087473335</v>
       </c>
       <c r="G56" s="9">
-        <f>F56</f>
+        <f t="shared" si="5"/>
         <v>43.584273087473335</v>
       </c>
       <c r="H56" s="40"/>
@@ -2490,7 +2489,7 @@
       <c r="J56" s="40"/>
       <c r="K56" s="46"/>
     </row>
-    <row r="57" spans="1:18" s="41" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" s="41" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A57" s="42"/>
       <c r="B57" s="43" t="s">
         <v>58</v>
@@ -2506,11 +2505,11 @@
         <v>4.43</v>
       </c>
       <c r="F57" s="45">
-        <f>PRODUCT(C57:E57)</f>
+        <f t="shared" si="4"/>
         <v>32.404754647973178</v>
       </c>
       <c r="G57" s="9">
-        <f>F57</f>
+        <f t="shared" si="5"/>
         <v>32.404754647973178</v>
       </c>
       <c r="H57" s="40"/>
@@ -2518,7 +2517,7 @@
       <c r="J57" s="40"/>
       <c r="K57" s="46"/>
     </row>
-    <row r="58" spans="1:18" s="41" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" s="41" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A58" s="42"/>
       <c r="B58" s="43" t="s">
         <v>58</v>
@@ -2534,11 +2533,11 @@
         <v>4.43</v>
       </c>
       <c r="F58" s="45">
-        <f>PRODUCT(C58:E58)</f>
+        <f t="shared" si="4"/>
         <v>22.062237122828403</v>
       </c>
       <c r="G58" s="9">
-        <f>F58</f>
+        <f t="shared" si="5"/>
         <v>22.062237122828403</v>
       </c>
       <c r="H58" s="40"/>
@@ -2546,7 +2545,7 @@
       <c r="J58" s="40"/>
       <c r="K58" s="46"/>
     </row>
-    <row r="59" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="42"/>
       <c r="B59" s="43"/>
       <c r="C59" s="44"/>
@@ -2559,7 +2558,7 @@
       <c r="J59" s="40"/>
       <c r="K59" s="46"/>
     </row>
-    <row r="60" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="B60" s="43" t="s">
         <v>48</v>
@@ -2584,7 +2583,7 @@
       </c>
       <c r="K60" s="5"/>
     </row>
-    <row r="61" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2"/>
       <c r="B61" s="43" t="s">
         <v>50</v>
@@ -2602,7 +2601,7 @@
       </c>
       <c r="K61" s="5"/>
     </row>
-    <row r="62" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2"/>
       <c r="B62" s="43"/>
       <c r="C62" s="3"/>
@@ -2615,7 +2614,7 @@
       <c r="J62" s="40"/>
       <c r="K62" s="5"/>
     </row>
-    <row r="63" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2"/>
       <c r="B63" s="43"/>
       <c r="C63" s="3"/>
@@ -2628,7 +2627,7 @@
       <c r="J63" s="40"/>
       <c r="K63" s="5"/>
     </row>
-    <row r="64" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2"/>
       <c r="B64" s="43"/>
       <c r="C64" s="3"/>
@@ -2641,7 +2640,7 @@
       <c r="J64" s="40"/>
       <c r="K64" s="5"/>
     </row>
-    <row r="65" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2"/>
       <c r="B65" s="43"/>
       <c r="C65" s="3"/>
@@ -2654,7 +2653,7 @@
       <c r="J65" s="40"/>
       <c r="K65" s="5"/>
     </row>
-    <row r="66" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2"/>
       <c r="B66" s="43"/>
       <c r="C66" s="3"/>
@@ -2667,7 +2666,7 @@
       <c r="J66" s="40"/>
       <c r="K66" s="5"/>
     </row>
-    <row r="67" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2"/>
       <c r="B67" s="43"/>
       <c r="C67" s="3"/>
@@ -2680,7 +2679,7 @@
       <c r="J67" s="40"/>
       <c r="K67" s="5"/>
     </row>
-    <row r="68" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2"/>
       <c r="B68" s="43"/>
       <c r="C68" s="3"/>
@@ -2693,7 +2692,7 @@
       <c r="J68" s="40"/>
       <c r="K68" s="5"/>
     </row>
-    <row r="69" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2"/>
       <c r="B69" s="43"/>
       <c r="C69" s="3"/>
@@ -2706,7 +2705,7 @@
       <c r="J69" s="40"/>
       <c r="K69" s="5"/>
     </row>
-    <row r="70" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2"/>
       <c r="B70" s="43"/>
       <c r="C70" s="3"/>
@@ -2719,7 +2718,7 @@
       <c r="J70" s="40"/>
       <c r="K70" s="5"/>
     </row>
-    <row r="71" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>6</v>
       </c>
@@ -2733,7 +2732,7 @@
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
       <c r="G71" s="7">
-        <f t="shared" ref="G71" si="4">PRODUCT(C71:F71)</f>
+        <f t="shared" ref="G71" si="6">PRODUCT(C71:F71)</f>
         <v>1</v>
       </c>
       <c r="H71" s="7" t="s">
@@ -2748,7 +2747,7 @@
       </c>
       <c r="K71" s="5"/>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="2"/>
       <c r="B72" s="8"/>
       <c r="C72" s="3"/>
@@ -2761,7 +2760,7 @@
       <c r="J72" s="18"/>
       <c r="K72" s="5"/>
     </row>
-    <row r="73" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>7</v>
       </c>
@@ -2775,7 +2774,7 @@
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="7">
-        <f t="shared" ref="G73" si="5">PRODUCT(C73:F73)</f>
+        <f t="shared" ref="G73" si="7">PRODUCT(C73:F73)</f>
         <v>1</v>
       </c>
       <c r="H73" s="7" t="s">
@@ -2790,7 +2789,7 @@
       </c>
       <c r="K73" s="5"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="2"/>
       <c r="B74" s="8"/>
       <c r="C74" s="3"/>
@@ -2803,7 +2802,7 @@
       <c r="J74" s="18"/>
       <c r="K74" s="5"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="21"/>
       <c r="B75" s="22" t="s">
         <v>22</v>
@@ -2821,7 +2820,7 @@
       </c>
       <c r="K75" s="25"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="M76" s="20"/>
       <c r="N76" s="20"/>
       <c r="O76" s="20"/>
@@ -2830,16 +2829,16 @@
       <c r="R76" s="20"/>
       <c r="S76" s="20"/>
     </row>
-    <row r="77" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="26"/>
       <c r="B77" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="54">
+      <c r="C77" s="48">
         <f>J75</f>
         <v>833549.84246881248</v>
       </c>
-      <c r="D77" s="55"/>
+      <c r="D77" s="49"/>
       <c r="E77" s="9">
         <v>100</v>
       </c>
@@ -2857,72 +2856,79 @@
       <c r="R77" s="19"/>
       <c r="S77" s="19"/>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B78" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="58">
+      <c r="C78" s="52">
         <v>700000</v>
       </c>
-      <c r="D78" s="59"/>
+      <c r="D78" s="53"/>
       <c r="E78" s="9"/>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B79" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C79" s="58">
+      <c r="C79" s="52">
         <f>C78-C81-C82</f>
         <v>665000</v>
       </c>
-      <c r="D79" s="59"/>
+      <c r="D79" s="53"/>
       <c r="E79" s="9">
         <f>C79/C77*100</f>
         <v>79.779272470425937</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B80" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C80" s="60">
+      <c r="C80" s="54">
         <f>C77-C79</f>
         <v>168549.84246881248</v>
       </c>
-      <c r="D80" s="60"/>
+      <c r="D80" s="54"/>
       <c r="E80" s="9">
         <f>100-E79</f>
         <v>20.220727529574063</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C81" s="54">
+      <c r="C81" s="48">
         <f>C78*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D81" s="55"/>
+      <c r="D81" s="49"/>
       <c r="E81" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C82" s="54">
+      <c r="C82" s="48">
         <f>C78*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D82" s="55"/>
+      <c r="D82" s="49"/>
       <c r="E82" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="C82:D82"/>
     <mergeCell ref="A7:F7"/>
@@ -2931,13 +2937,6 @@
     <mergeCell ref="C78:D78"/>
     <mergeCell ref="C79:D79"/>
     <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
